--- a/docs/算定テスト_10世帯.xlsx
+++ b/docs/算定テスト_10世帯.xlsx
@@ -11,6 +11,7 @@
     <sheet name="テスト結果" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="医療判定" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="パラメータ" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="教育費(段階別)" sheetId="4" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -3878,6 +3879,13 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-23 更新：教育費を段階別モデル（対応コミット 60dbe72・2026-08-23）に追随。GT-02・GT-06 の教育費／必要額／提示レンジを「教育費(段階別)」シートの式から引き直した。他8世帯は不変。</t>
+        </is>
+      </c>
+    </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>3</v>
@@ -4121,8 +4129,9 @@
       <c r="G8" s="7" t="n">
         <v>1680</v>
       </c>
-      <c r="H8" s="7" t="n">
-        <v>1682</v>
+      <c r="H8" s="7">
+        <f>'教育費(段階別)'!D19</f>
+        <v>1575</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0</v>
@@ -4132,7 +4141,7 @@
       </c>
       <c r="K8" s="8" t="n">
         <f aca="false">SUM(F8:J8)</f>
-        <v>8266</v>
+        <v>8159</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>2063</v>
@@ -4155,13 +4164,15 @@
       </c>
       <c r="R8" s="8" t="n">
         <f aca="false">MAX(0,K8-Q8)</f>
-        <v>2571</v>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>2100</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>3100</v>
+        <v>2464</v>
+      </c>
+      <c r="S8" s="7">
+        <f>ROUND(R8*0.8/100,0)*100</f>
+        <v>2000</v>
+      </c>
+      <c r="T8" s="7">
+        <f>ROUND(R8*1.2/100,0)*100</f>
+        <v>3000</v>
       </c>
       <c r="U8" s="10" t="s">
         <v>33</v>
@@ -4171,7 +4182,7 @@
       </c>
       <c r="W8" s="7" t="n">
         <f aca="false">IF(V8="","",V8-S8)</f>
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4646,8 +4657,9 @@
       <c r="G15" s="7" t="n">
         <v>2160</v>
       </c>
-      <c r="H15" s="7" t="n">
-        <v>455</v>
+      <c r="H15" s="7">
+        <f>'教育費(段階別)'!D20</f>
+        <v>549</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0</v>
@@ -4657,7 +4669,7 @@
       </c>
       <c r="K15" s="8" t="n">
         <f aca="false">SUM(F15:J15)</f>
-        <v>5335</v>
+        <v>5429</v>
       </c>
       <c r="L15" s="7" t="n">
         <v>655</v>
@@ -4680,13 +4692,15 @@
       </c>
       <c r="R15" s="8" t="n">
         <f aca="false">MAX(0,K15-Q15)</f>
-        <v>1963</v>
-      </c>
-      <c r="S15" s="7" t="n">
+        <v>2057</v>
+      </c>
+      <c r="S15" s="7">
+        <f>ROUND(R15*0.8/100,0)*100</f>
         <v>1600</v>
       </c>
-      <c r="T15" s="7" t="n">
-        <v>2400</v>
+      <c r="T15" s="7">
+        <f>ROUND(R15*1.2/100,0)*100</f>
+        <v>2500</v>
       </c>
       <c r="U15" s="10" t="s">
         <v>33</v>
@@ -6310,4 +6324,404 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">教育費（段階別モデル）の検算 ─ 機能仕様書 §4.2.2 / params.education</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対応コミット 60dbe72（2026-08-23 教育費を段階別に作り替える）／再構築 2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">出典：文科省「令和5年度 子供の学習費調査」学習費総額（塾・部活・行事・制服を含む実支出）。高校は就学支援金を控除。大学は4年総額÷4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">段階</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">開始年齢</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了年齢</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公立 年額(円)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">私立 年額(円)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">就学支援金(円)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幼稚園</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>184644</v>
+      </c>
+      <c r="E6">
+        <v>347338</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小学校</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>336265</v>
+      </c>
+      <c r="E7">
+        <v>1828112</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中学校</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>542475</v>
+      </c>
+      <c r="E8">
+        <v>1560359</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高校</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>597752</v>
+      </c>
+      <c r="E9">
+        <v>1030283</v>
+      </c>
+      <c r="F9">
+        <v>118800</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大学</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>606300</v>
+      </c>
+      <c r="E10">
+        <v>1417500</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地域係数</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>1.0</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">当面 1.0（全国平均）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公立中心（幼=公立/小=公立/中=公立/高=公立/大=国立）の年額。年齢ごとに段階を引く</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">年齢</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15">
+        <v>7</v>
+      </c>
+      <c r="J15">
+        <v>8</v>
+      </c>
+      <c r="K15">
+        <v>9</v>
+      </c>
+      <c r="L15">
+        <v>10</v>
+      </c>
+      <c r="M15">
+        <v>11</v>
+      </c>
+      <c r="N15">
+        <v>12</v>
+      </c>
+      <c r="O15">
+        <v>13</v>
+      </c>
+      <c r="P15">
+        <v>14</v>
+      </c>
+      <c r="Q15">
+        <v>15</v>
+      </c>
+      <c r="R15">
+        <v>16</v>
+      </c>
+      <c r="S15">
+        <v>17</v>
+      </c>
+      <c r="T15">
+        <v>18</v>
+      </c>
+      <c r="U15">
+        <v>19</v>
+      </c>
+      <c r="V15">
+        <v>20</v>
+      </c>
+      <c r="W15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公立中心の年額(円)</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>0</f>
+      </c>
+      <c r="C16">
+        <f>0</f>
+      </c>
+      <c r="D16">
+        <f>0</f>
+      </c>
+      <c r="E16">
+        <f>($D$6-$F$6)*$B$12</f>
+      </c>
+      <c r="F16">
+        <f>($D$6-$F$6)*$B$12</f>
+      </c>
+      <c r="G16">
+        <f>($D$6-$F$6)*$B$12</f>
+      </c>
+      <c r="H16">
+        <f>($D$7-$F$7)*$B$12</f>
+      </c>
+      <c r="I16">
+        <f>($D$7-$F$7)*$B$12</f>
+      </c>
+      <c r="J16">
+        <f>($D$7-$F$7)*$B$12</f>
+      </c>
+      <c r="K16">
+        <f>($D$7-$F$7)*$B$12</f>
+      </c>
+      <c r="L16">
+        <f>($D$7-$F$7)*$B$12</f>
+      </c>
+      <c r="M16">
+        <f>($D$7-$F$7)*$B$12</f>
+      </c>
+      <c r="N16">
+        <f>($D$8-$F$8)*$B$12</f>
+      </c>
+      <c r="O16">
+        <f>($D$8-$F$8)*$B$12</f>
+      </c>
+      <c r="P16">
+        <f>($D$8-$F$8)*$B$12</f>
+      </c>
+      <c r="Q16">
+        <f>($D$9-$F$9)*$B$12</f>
+      </c>
+      <c r="R16">
+        <f>($D$9-$F$9)*$B$12</f>
+      </c>
+      <c r="S16">
+        <f>($D$9-$F$9)*$B$12</f>
+      </c>
+      <c r="T16">
+        <f>$D$10*$B$12</f>
+      </c>
+      <c r="U16">
+        <f>$D$10*$B$12</f>
+      </c>
+      <c r="V16">
+        <f>$D$10*$B$12</f>
+      </c>
+      <c r="W16">
+        <f>$D$10*$B$12</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">世帯</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子の現年齢</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">教育費(円)＝現年齢〜21歳の合計</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">教育費(万円)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GT-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5歳・2歳</t>
+        </is>
+      </c>
+      <c r="C19">
+        <f>SUM(G$16:W$16)+SUM(D$16:W$16)</f>
+        <v>15752718</v>
+      </c>
+      <c r="D19">
+        <f>ROUND(C19/10000,0)</f>
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GT-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12歳</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>SUM(N$16:W$16)</f>
+        <v>5489481</v>
+      </c>
+      <c r="D20">
+        <f>ROUND(C20/10000,0)</f>
+        <v>549</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/docs/算定テスト_10世帯.xlsx
+++ b/docs/算定テスト_10世帯.xlsx
@@ -3882,7 +3882,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-23 更新：教育費を段階別モデル（対応コミット 60dbe72・2026-08-23）に追随。GT-02・GT-06 の教育費／必要額／提示レンジを「教育費(段階別)」シートの式から引き直した。他8世帯は不変。</t>
+          <t xml:space="preserve">2026-09-23再構築（60dbe72追随・検算自体は8/23に人が実施済み）。教育費を段階別モデル（対応コミット 60dbe72・2026-08-23）に追随。GT-02・GT-06 の教育費／必要額／提示レンジを「教育費(段階別)」シートの式から引き直した。他8世帯は不変。</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">対応コミット 60dbe72（2026-08-23 教育費を段階別に作り替える）／再構築 2026-09-23</t>
+          <t xml:space="preserve">2026-09-23再構築（60dbe72追随・検算自体は8/23に人が実施済み）。対応コミット 60dbe72（2026-08-23 教育費を段階別に作り替える）。ファイルへの反映だけが漏れていた</t>
         </is>
       </c>
     </row>
